--- a/artfynd/A 33462-2026 artfynd.xlsx
+++ b/artfynd/A 33462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416592</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416590</v>
       </c>
       <c r="B3" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416589</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416591</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416615</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137416610</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137416593</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137416594</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>137416595</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137416597</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137416598</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>137416601</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>137416602</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>137416603</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>137416604</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>137416606</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>137416607</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>137416608</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>137416609</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137416611</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>137416612</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137416613</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137416614</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33462-2026 artfynd.xlsx
+++ b/artfynd/A 33462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416592</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416590</v>
       </c>
       <c r="B3" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416589</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416591</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416615</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137416610</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137416593</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137416594</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>137416595</v>
       </c>
       <c r="B12" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137416597</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137416598</v>
       </c>
       <c r="B14" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>137416601</v>
       </c>
       <c r="B15" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>137416602</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>137416603</v>
       </c>
       <c r="B17" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>137416604</v>
       </c>
       <c r="B18" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>137416606</v>
       </c>
       <c r="B19" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>137416607</v>
       </c>
       <c r="B20" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>137416608</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>137416609</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137416611</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>137416612</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137416613</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137416614</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33462-2026 artfynd.xlsx
+++ b/artfynd/A 33462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416592</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416590</v>
       </c>
       <c r="B3" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416589</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416591</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416615</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137416610</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137416593</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137416594</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>137416595</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137416597</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137416598</v>
       </c>
       <c r="B14" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>137416601</v>
       </c>
       <c r="B15" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>137416602</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>137416603</v>
       </c>
       <c r="B17" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>137416604</v>
       </c>
       <c r="B18" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>137416606</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>137416607</v>
       </c>
       <c r="B20" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>137416608</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>137416609</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137416611</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>137416612</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137416613</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137416614</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33462-2026 artfynd.xlsx
+++ b/artfynd/A 33462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416592</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416590</v>
       </c>
       <c r="B3" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416589</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416591</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416615</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137416610</v>
       </c>
       <c r="B7" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137416605</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137416600</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137416593</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137416594</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>137416595</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137416597</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>137416598</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>137416601</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>137416602</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>137416603</v>
       </c>
       <c r="B17" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>137416604</v>
       </c>
       <c r="B18" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>137416606</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>137416607</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>137416608</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>137416609</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137416611</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>137416612</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137416613</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137416614</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
